--- a/src/202401012_fixed_temp_zf_ovary.xlsx
+++ b/src/202401012_fixed_temp_zf_ovary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\其他電腦\My Computer\GlycoMSParser\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCF6886-4BEF-4CF4-86DA-48E96B84BFC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD65CD71-60CF-4907-8AD5-BEA78DF5C7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{67B4FEEB-0D84-F241-9CC2-FB10DE711B8D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{67B4FEEB-0D84-F241-9CC2-FB10DE711B8D}"/>
   </bookViews>
   <sheets>
     <sheet name="Glycanlist" sheetId="1" r:id="rId1"/>
@@ -137,10 +137,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">peak </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MS2 in Na</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -905,6 +901,10 @@
   </si>
   <si>
     <t>Change H5N2~H9N2 to annotation Man5~Man9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peak</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1628,10 +1628,10 @@
         <v>11</v>
       </c>
       <c r="H1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J1" t="s">
         <v>20</v>
@@ -1643,13 +1643,13 @@
         <v>21</v>
       </c>
       <c r="M1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -1692,7 +1692,7 @@
         <v>-1</v>
       </c>
       <c r="N2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P2" t="s">
         <v>12</v>
@@ -1751,7 +1751,7 @@
         <v>-1</v>
       </c>
       <c r="N3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1796,7 +1796,7 @@
         <v>-1</v>
       </c>
       <c r="N4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1841,7 +1841,7 @@
         <v>-1</v>
       </c>
       <c r="N5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1886,7 +1886,7 @@
         <v>-1</v>
       </c>
       <c r="N6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1894,10 +1894,10 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7">
         <f t="shared" si="2"/>
@@ -1934,15 +1934,15 @@
         <v>-1</v>
       </c>
       <c r="N7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="B8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8">
         <f t="shared" si="2"/>
@@ -1979,7 +1979,7 @@
         <v>-1</v>
       </c>
       <c r="N8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1987,10 +1987,10 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9">
         <f t="shared" si="2"/>
@@ -2027,21 +2027,21 @@
         <v>-1</v>
       </c>
       <c r="N9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D10">
         <f t="shared" si="2"/>
@@ -2078,10 +2078,10 @@
         <v>-1</v>
       </c>
       <c r="N10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2089,10 +2089,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D11">
         <f t="shared" si="2"/>
@@ -2129,15 +2129,15 @@
         <v>-1</v>
       </c>
       <c r="N11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="B12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D12">
         <f t="shared" si="2"/>
@@ -2174,7 +2174,7 @@
         <v>-1</v>
       </c>
       <c r="N12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2182,10 +2182,10 @@
         <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D13">
         <f t="shared" si="2"/>
@@ -2222,7 +2222,7 @@
         <v>-1</v>
       </c>
       <c r="N13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -2230,10 +2230,10 @@
         <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D14">
         <f t="shared" si="2"/>
@@ -2270,7 +2270,7 @@
         <v>-1</v>
       </c>
       <c r="N14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2278,10 +2278,10 @@
         <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D15">
         <f t="shared" si="2"/>
@@ -2318,15 +2318,15 @@
         <v>-1</v>
       </c>
       <c r="N15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="B16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D16">
         <f t="shared" si="2"/>
@@ -2363,7 +2363,7 @@
         <v>-1</v>
       </c>
       <c r="N16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -2371,10 +2371,10 @@
         <v>77</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17">
         <f t="shared" si="2"/>
@@ -2411,7 +2411,7 @@
         <v>-1</v>
       </c>
       <c r="N17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:15">
@@ -2419,10 +2419,10 @@
         <v>81</v>
       </c>
       <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" t="s">
         <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>77</v>
       </c>
       <c r="D18">
         <f t="shared" si="2"/>
@@ -2459,7 +2459,7 @@
         <v>-1</v>
       </c>
       <c r="N18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -2467,10 +2467,10 @@
         <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D19">
         <f t="shared" si="2"/>
@@ -2507,10 +2507,10 @@
         <v>-1</v>
       </c>
       <c r="N19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -2518,10 +2518,10 @@
         <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D20">
         <f t="shared" si="2"/>
@@ -2558,7 +2558,7 @@
         <v>-1</v>
       </c>
       <c r="N20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -2566,10 +2566,10 @@
         <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D21">
         <f t="shared" si="2"/>
@@ -2606,7 +2606,7 @@
         <v>-1</v>
       </c>
       <c r="N21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -2614,10 +2614,10 @@
         <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D22">
         <f t="shared" si="2"/>
@@ -2654,7 +2654,7 @@
         <v>-1</v>
       </c>
       <c r="N22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -2662,10 +2662,10 @@
         <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D23">
         <f t="shared" si="2"/>
@@ -2702,7 +2702,7 @@
         <v>-1</v>
       </c>
       <c r="N23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -2710,10 +2710,10 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D24">
         <f t="shared" si="2"/>
@@ -2750,15 +2750,15 @@
         <v>-1</v>
       </c>
       <c r="N24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="B25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D25">
         <f t="shared" si="2"/>
@@ -2795,18 +2795,18 @@
         <v>-1</v>
       </c>
       <c r="N25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D26">
         <f t="shared" si="2"/>
@@ -2843,7 +2843,7 @@
         <v>-1</v>
       </c>
       <c r="N26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:15">
@@ -2851,10 +2851,10 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D27">
         <f t="shared" si="2"/>
@@ -2891,10 +2891,10 @@
         <v>-1</v>
       </c>
       <c r="N27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:15">
@@ -2902,10 +2902,10 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D28">
         <f t="shared" si="2"/>
@@ -2942,10 +2942,10 @@
         <v>-1</v>
       </c>
       <c r="N28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:15">
@@ -2953,10 +2953,10 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" t="s">
         <v>97</v>
-      </c>
-      <c r="C29" t="s">
-        <v>98</v>
       </c>
       <c r="D29">
         <f t="shared" si="2"/>
@@ -2993,18 +2993,18 @@
         <v>-1</v>
       </c>
       <c r="O29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" t="s">
         <v>99</v>
-      </c>
-      <c r="B30" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" t="s">
-        <v>100</v>
       </c>
       <c r="D30">
         <f t="shared" si="2"/>
@@ -3041,10 +3041,10 @@
         <v>-1</v>
       </c>
       <c r="N30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:15">
@@ -3052,10 +3052,10 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <f t="shared" si="2"/>
@@ -3092,21 +3092,21 @@
         <v>-1</v>
       </c>
       <c r="N31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D32">
         <f t="shared" si="2"/>
@@ -3143,10 +3143,10 @@
         <v>-1</v>
       </c>
       <c r="N32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:15">
@@ -3154,10 +3154,10 @@
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D33">
         <f t="shared" ref="D33:D37" si="4">E33+21.9819</f>
@@ -3194,21 +3194,21 @@
         <v>-1</v>
       </c>
       <c r="N33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D34">
         <f t="shared" si="4"/>
@@ -3245,21 +3245,21 @@
         <v>-1</v>
       </c>
       <c r="N34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" t="s">
         <v>114</v>
       </c>
-      <c r="B35" t="s">
-        <v>115</v>
-      </c>
       <c r="C35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D35">
         <f t="shared" si="4"/>
@@ -3296,10 +3296,10 @@
         <v>-1</v>
       </c>
       <c r="N35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O35" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:15">
@@ -3307,10 +3307,10 @@
         <v>23</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D36">
         <f t="shared" si="4"/>
@@ -3347,21 +3347,21 @@
         <v>-1</v>
       </c>
       <c r="N36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O36" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C37" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D37">
         <f t="shared" si="4"/>
@@ -3398,18 +3398,18 @@
         <v>-1</v>
       </c>
       <c r="N37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D38">
         <f t="shared" ref="D38:D40" si="7">E38+21.9819</f>
@@ -3446,18 +3446,18 @@
         <v>-1</v>
       </c>
       <c r="N38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C39" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D39">
         <f t="shared" si="7"/>
@@ -3494,18 +3494,18 @@
         <v>-1</v>
       </c>
       <c r="N39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:15">
       <c r="A40" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D40">
         <f t="shared" si="7"/>
@@ -3542,21 +3542,21 @@
         <v>-1</v>
       </c>
       <c r="N40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C41" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D41">
         <f t="shared" ref="D41:D44" si="10">E41+21.9819</f>
@@ -3593,21 +3593,21 @@
         <v>-1</v>
       </c>
       <c r="N41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:15">
       <c r="A42" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C42" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D42">
         <f t="shared" si="10"/>
@@ -3644,18 +3644,18 @@
         <v>-1</v>
       </c>
       <c r="N42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:15">
       <c r="A43" t="s">
+        <v>132</v>
+      </c>
+      <c r="B43" t="s">
         <v>133</v>
       </c>
-      <c r="B43" t="s">
-        <v>134</v>
-      </c>
       <c r="C43" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D43">
         <f t="shared" si="10"/>
@@ -3692,7 +3692,7 @@
         <v>-1</v>
       </c>
       <c r="N43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:15">
@@ -3700,10 +3700,10 @@
         <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C44" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D44">
         <f t="shared" si="10"/>
@@ -3740,10 +3740,10 @@
         <v>-1</v>
       </c>
       <c r="N44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O44" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:15">
@@ -3751,10 +3751,10 @@
         <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C45" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D45">
         <f t="shared" ref="D45:D52" si="13">E45+21.9819</f>
@@ -3791,15 +3791,15 @@
         <v>-1</v>
       </c>
       <c r="N45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:15">
       <c r="A46" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" t="s">
         <v>139</v>
-      </c>
-      <c r="C46" t="s">
-        <v>140</v>
       </c>
       <c r="D46">
         <f t="shared" si="13"/>
@@ -3836,10 +3836,10 @@
         <v>-1</v>
       </c>
       <c r="N46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:15">
@@ -3847,10 +3847,10 @@
         <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D47">
         <f t="shared" si="13"/>
@@ -3887,10 +3887,10 @@
         <v>-1</v>
       </c>
       <c r="N47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O47" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="48" spans="1:15">
@@ -3898,7 +3898,7 @@
         <v>60</v>
       </c>
       <c r="C48" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D48">
         <f t="shared" si="13"/>
@@ -3935,10 +3935,10 @@
         <v>-1</v>
       </c>
       <c r="N48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O48" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="1:15">
@@ -3946,10 +3946,10 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D49">
         <f t="shared" si="13"/>
@@ -3986,18 +3986,18 @@
         <v>-1</v>
       </c>
       <c r="N49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:15">
       <c r="A50" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C50" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D50">
         <f t="shared" si="13"/>
@@ -4034,7 +4034,7 @@
         <v>-1</v>
       </c>
       <c r="N50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:15">
@@ -4042,7 +4042,7 @@
         <v>65</v>
       </c>
       <c r="C51" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D51">
         <f t="shared" si="13"/>
@@ -4079,7 +4079,7 @@
         <v>-1</v>
       </c>
       <c r="N51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:15">
@@ -4087,7 +4087,7 @@
         <v>66</v>
       </c>
       <c r="C52" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D52">
         <f t="shared" si="13"/>
@@ -4124,18 +4124,18 @@
         <v>-1</v>
       </c>
       <c r="N52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:15">
       <c r="A53" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D53">
         <f t="shared" ref="D53:D63" si="16">E53+21.9819</f>
@@ -4172,15 +4172,15 @@
         <v>-1</v>
       </c>
       <c r="N53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O53" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" spans="1:15">
       <c r="C54" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D54">
         <f t="shared" ref="D54" si="19">E54+21.9819</f>
@@ -4217,21 +4217,21 @@
         <v>-1</v>
       </c>
       <c r="N54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O54" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" spans="1:15">
       <c r="A55" t="s">
+        <v>151</v>
+      </c>
+      <c r="B55" t="s">
+        <v>147</v>
+      </c>
+      <c r="C55" t="s">
         <v>152</v>
-      </c>
-      <c r="B55" t="s">
-        <v>148</v>
-      </c>
-      <c r="C55" t="s">
-        <v>153</v>
       </c>
       <c r="D55">
         <f t="shared" si="16"/>
@@ -4268,12 +4268,12 @@
         <v>-1</v>
       </c>
       <c r="N55" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:15">
       <c r="C56" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D56">
         <f t="shared" ref="D56" si="23">E56+21.9819</f>
@@ -4310,21 +4310,21 @@
         <v>-1</v>
       </c>
       <c r="N56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O56" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:15">
       <c r="A57" t="s">
+        <v>154</v>
+      </c>
+      <c r="B57" t="s">
         <v>155</v>
       </c>
-      <c r="B57" t="s">
-        <v>156</v>
-      </c>
       <c r="C57" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D57">
         <f t="shared" si="16"/>
@@ -4361,10 +4361,10 @@
         <v>-1</v>
       </c>
       <c r="N57" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O57" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="58" spans="1:15">
@@ -4372,10 +4372,10 @@
         <v>74</v>
       </c>
       <c r="B58" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C58" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D58">
         <f t="shared" si="16"/>
@@ -4412,18 +4412,18 @@
         <v>-1</v>
       </c>
       <c r="N58" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:15">
       <c r="A59" t="s">
+        <v>157</v>
+      </c>
+      <c r="B59" t="s">
+        <v>147</v>
+      </c>
+      <c r="C59" t="s">
         <v>158</v>
-      </c>
-      <c r="B59" t="s">
-        <v>148</v>
-      </c>
-      <c r="C59" t="s">
-        <v>159</v>
       </c>
       <c r="D59">
         <f t="shared" si="16"/>
@@ -4460,15 +4460,15 @@
         <v>-1</v>
       </c>
       <c r="N59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O59" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="60" spans="1:15">
       <c r="C60" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D60">
         <f t="shared" ref="D60:D61" si="27">E60+21.9819</f>
@@ -4505,10 +4505,10 @@
         <v>-1</v>
       </c>
       <c r="N60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O60" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="61" spans="1:15">
@@ -4516,10 +4516,10 @@
         <v>78</v>
       </c>
       <c r="B61" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C61" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D61">
         <f t="shared" si="27"/>
@@ -4556,12 +4556,12 @@
         <v>-1</v>
       </c>
       <c r="N61" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:15" s="9" customFormat="1">
       <c r="C62" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D62" s="9">
         <f t="shared" si="16"/>
@@ -4598,21 +4598,21 @@
         <v>-1</v>
       </c>
       <c r="N62" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O62" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="1:15">
       <c r="A63" t="s">
+        <v>160</v>
+      </c>
+      <c r="B63" t="s">
+        <v>162</v>
+      </c>
+      <c r="C63" t="s">
         <v>161</v>
-      </c>
-      <c r="B63" t="s">
-        <v>163</v>
-      </c>
-      <c r="C63" t="s">
-        <v>162</v>
       </c>
       <c r="D63">
         <f t="shared" si="16"/>
@@ -4649,10 +4649,10 @@
         <v>-1</v>
       </c>
       <c r="N63" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O63" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="64" spans="1:15">
@@ -4660,10 +4660,10 @@
         <v>86</v>
       </c>
       <c r="B64" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C64" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D64">
         <f t="shared" ref="D64:D65" si="31">E64+21.9819</f>
@@ -4700,18 +4700,18 @@
         <v>-1</v>
       </c>
       <c r="N64" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:15">
       <c r="A65" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B65" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D65">
         <f t="shared" si="31"/>
@@ -4748,7 +4748,7 @@
         <v>-1</v>
       </c>
       <c r="N65" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:15">
@@ -4756,7 +4756,7 @@
         <v>92</v>
       </c>
       <c r="C66" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D66">
         <f t="shared" ref="D66:D69" si="34">E66+21.9819</f>
@@ -4793,7 +4793,7 @@
         <v>-1</v>
       </c>
       <c r="N66" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:15">
@@ -4801,10 +4801,10 @@
         <v>93</v>
       </c>
       <c r="B67" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D67">
         <f t="shared" si="34"/>
@@ -4841,7 +4841,7 @@
         <v>0</v>
       </c>
       <c r="N67" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:15">
@@ -4849,10 +4849,10 @@
         <v>94</v>
       </c>
       <c r="B68" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C68" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D68">
         <f t="shared" si="34"/>
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:15">
@@ -4897,10 +4897,10 @@
         <v>95</v>
       </c>
       <c r="B69" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C69" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D69">
         <f t="shared" si="34"/>
@@ -4937,10 +4937,10 @@
         <v>0</v>
       </c>
       <c r="N69" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O69" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -4960,34 +4960,34 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
         <v>191</v>
       </c>
-      <c r="C1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" t="s">
-        <v>192</v>
-      </c>
       <c r="G1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H1" t="s">
+        <v>216</v>
+      </c>
+      <c r="I1" t="s">
         <v>218</v>
       </c>
-      <c r="H1" t="s">
-        <v>217</v>
-      </c>
-      <c r="I1" t="s">
-        <v>219</v>
-      </c>
       <c r="J1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5027,7 +5027,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5047,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5067,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -5087,7 +5087,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -5107,7 +5107,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -5127,7 +5127,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -5167,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -5187,7 +5187,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5227,7 +5227,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -5267,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -5287,7 +5287,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5307,7 +5307,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5327,7 +5327,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -5347,7 +5347,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -5367,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -5387,7 +5387,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -5407,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5427,7 +5427,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5447,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -5487,7 +5487,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -5527,7 +5527,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -5547,7 +5547,7 @@
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -5567,7 +5567,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -5587,7 +5587,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -5607,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -5627,7 +5627,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -5647,7 +5647,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -5667,7 +5667,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -5687,7 +5687,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -5707,7 +5707,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -5727,12 +5727,12 @@
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B39">
         <v>15761</v>
@@ -5747,12 +5747,12 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B40">
         <v>15961</v>
@@ -5767,12 +5767,12 @@
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41">
         <v>16128</v>
@@ -5787,12 +5787,12 @@
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42">
         <v>16328</v>
@@ -5807,12 +5807,12 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B43">
         <v>17241</v>
@@ -5827,12 +5827,12 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B44">
         <v>17458</v>
@@ -5847,12 +5847,12 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45">
         <v>15686</v>
@@ -5867,12 +5867,12 @@
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B46">
         <v>15757</v>
@@ -5887,12 +5887,12 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B47">
         <v>15921</v>
@@ -5907,12 +5907,12 @@
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48">
         <v>16260</v>
@@ -5927,12 +5927,12 @@
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49">
         <v>16433</v>
@@ -5947,12 +5947,12 @@
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B50">
         <v>17170</v>
@@ -5967,12 +5967,12 @@
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B51">
         <v>17345</v>
@@ -5987,12 +5987,12 @@
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B52">
         <v>15967</v>
@@ -6007,12 +6007,12 @@
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B53">
         <v>16149</v>
@@ -6027,12 +6027,12 @@
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B54">
         <v>17462</v>
@@ -6047,12 +6047,12 @@
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55">
         <v>16081</v>
@@ -6067,12 +6067,12 @@
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B56">
         <v>16122</v>
@@ -6087,12 +6087,12 @@
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B57">
         <v>17507</v>
@@ -6107,12 +6107,12 @@
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58">
         <v>17600</v>
@@ -6127,12 +6127,12 @@
         <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59">
         <v>17883</v>
@@ -6147,12 +6147,12 @@
         <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B60">
         <v>18461</v>
@@ -6167,12 +6167,12 @@
         <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B61">
         <v>18640</v>
@@ -6187,12 +6187,12 @@
         <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B62">
         <v>18846</v>
@@ -6207,12 +6207,12 @@
         <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B63">
         <v>19015</v>
@@ -6227,12 +6227,12 @@
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B64">
         <v>19201</v>
@@ -6247,12 +6247,12 @@
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B65">
         <v>17348</v>
@@ -6267,12 +6267,12 @@
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B66">
         <v>17528</v>
@@ -6287,12 +6287,12 @@
         <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B67">
         <v>17709</v>
@@ -6307,12 +6307,12 @@
         <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B68">
         <v>17887</v>
@@ -6327,12 +6327,12 @@
         <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B69">
         <v>18108</v>
@@ -6347,12 +6347,12 @@
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B70">
         <v>18361</v>
@@ -6367,12 +6367,12 @@
         <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B71">
         <v>18634</v>
@@ -6387,12 +6387,12 @@
         <v>1</v>
       </c>
       <c r="F71" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B72">
         <v>18798</v>
@@ -6407,12 +6407,12 @@
         <v>1</v>
       </c>
       <c r="F72" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B73">
         <v>18973</v>
@@ -6427,12 +6427,12 @@
         <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B74">
         <v>19163</v>
@@ -6447,12 +6447,12 @@
         <v>1</v>
       </c>
       <c r="F74" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B75">
         <v>17346</v>
@@ -6467,12 +6467,12 @@
         <v>2</v>
       </c>
       <c r="F75" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B76">
         <v>17527</v>
@@ -6487,12 +6487,12 @@
         <v>1</v>
       </c>
       <c r="F76" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B77">
         <v>17708</v>
@@ -6507,12 +6507,12 @@
         <v>1</v>
       </c>
       <c r="F77" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B78">
         <v>17886</v>
@@ -6527,12 +6527,12 @@
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B79">
         <v>18663</v>
@@ -6547,12 +6547,12 @@
         <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B80">
         <v>18833</v>
@@ -6567,12 +6567,12 @@
         <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B81">
         <v>19009</v>
@@ -6587,12 +6587,12 @@
         <v>1</v>
       </c>
       <c r="F81" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B82">
         <v>19237</v>
@@ -6607,12 +6607,12 @@
         <v>1</v>
       </c>
       <c r="F82" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B83">
         <v>18978</v>
@@ -6627,12 +6627,12 @@
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B84">
         <v>19157</v>
@@ -6647,12 +6647,12 @@
         <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B85">
         <v>19335</v>
@@ -6667,12 +6667,12 @@
         <v>1</v>
       </c>
       <c r="F85" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B86">
         <v>19520</v>
@@ -6687,12 +6687,12 @@
         <v>1</v>
       </c>
       <c r="F86" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B87">
         <v>20422</v>
@@ -6707,12 +6707,12 @@
         <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B88">
         <v>20614</v>
@@ -6727,12 +6727,12 @@
         <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B89">
         <v>21512</v>
@@ -6747,12 +6747,12 @@
         <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B90">
         <v>21704</v>
@@ -6767,12 +6767,12 @@
         <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B91">
         <v>22881</v>
@@ -6787,12 +6787,12 @@
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B92">
         <v>21280</v>
@@ -6807,12 +6807,12 @@
         <v>1</v>
       </c>
       <c r="F92" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B93">
         <v>21474</v>
@@ -6827,12 +6827,12 @@
         <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B94">
         <v>21664</v>
@@ -6847,12 +6847,12 @@
         <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B95">
         <v>22410</v>
@@ -6867,12 +6867,12 @@
         <v>1</v>
       </c>
       <c r="F95" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B96">
         <v>22602</v>
@@ -6887,12 +6887,12 @@
         <v>1</v>
       </c>
       <c r="F96" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B97">
         <v>22808</v>
@@ -6907,12 +6907,12 @@
         <v>1</v>
       </c>
       <c r="F97" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B98">
         <v>15710</v>
@@ -6927,12 +6927,12 @@
         <v>1</v>
       </c>
       <c r="F98" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B99">
         <v>15883</v>
@@ -6947,12 +6947,12 @@
         <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B100">
         <v>16442</v>
@@ -6967,12 +6967,12 @@
         <v>2</v>
       </c>
       <c r="F100" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B101">
         <v>16959</v>
@@ -6987,12 +6987,12 @@
         <v>1</v>
       </c>
       <c r="F101" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B102">
         <v>17138</v>
@@ -7007,12 +7007,12 @@
         <v>1</v>
       </c>
       <c r="F102" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B103">
         <v>17316</v>
@@ -7027,12 +7027,12 @@
         <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B104">
         <v>15959</v>
@@ -7047,12 +7047,12 @@
         <v>1</v>
       </c>
       <c r="F104" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B105">
         <v>16146</v>
@@ -7067,12 +7067,12 @@
         <v>1</v>
       </c>
       <c r="F105" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B106">
         <v>16538</v>
@@ -7087,12 +7087,12 @@
         <v>1</v>
       </c>
       <c r="F106" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B107">
         <v>16596</v>
@@ -7107,12 +7107,12 @@
         <v>1</v>
       </c>
       <c r="F107" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B108">
         <v>16705</v>
@@ -7127,12 +7127,12 @@
         <v>1</v>
       </c>
       <c r="F108" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B109">
         <v>16891</v>
@@ -7147,12 +7147,12 @@
         <v>1</v>
       </c>
       <c r="F109" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B110">
         <v>17092</v>
@@ -7167,12 +7167,12 @@
         <v>1</v>
       </c>
       <c r="F110" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B111">
         <v>17309</v>
@@ -7187,12 +7187,12 @@
         <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B112">
         <v>15574</v>
@@ -7207,12 +7207,12 @@
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B113">
         <v>15745</v>
@@ -7227,12 +7227,12 @@
         <v>1</v>
       </c>
       <c r="F113" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B114">
         <v>15920</v>
@@ -7247,12 +7247,12 @@
         <v>1</v>
       </c>
       <c r="F114" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B115">
         <v>16107</v>
@@ -7267,12 +7267,12 @@
         <v>1</v>
       </c>
       <c r="F115" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B116">
         <v>16325</v>
@@ -7287,12 +7287,12 @@
         <v>1</v>
       </c>
       <c r="F116" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B117">
         <v>16690</v>
@@ -7307,12 +7307,12 @@
         <v>1</v>
       </c>
       <c r="F117" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B118">
         <v>16860</v>
@@ -7327,12 +7327,12 @@
         <v>1</v>
       </c>
       <c r="F118" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B119">
         <v>17062</v>
@@ -7347,12 +7347,12 @@
         <v>1</v>
       </c>
       <c r="F119" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B120">
         <v>17237</v>
@@ -7367,12 +7367,12 @@
         <v>1</v>
       </c>
       <c r="F120" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B121">
         <v>17531</v>
@@ -7387,12 +7387,12 @@
         <v>0</v>
       </c>
       <c r="F121" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B122">
         <v>15549</v>
@@ -7407,12 +7407,12 @@
         <v>1</v>
       </c>
       <c r="F122" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B123">
         <v>15716</v>
@@ -7427,12 +7427,12 @@
         <v>1</v>
       </c>
       <c r="F123" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B124">
         <v>15881</v>
@@ -7447,12 +7447,12 @@
         <v>1</v>
       </c>
       <c r="F124" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B125">
         <v>16076</v>
@@ -7467,12 +7467,12 @@
         <v>1</v>
       </c>
       <c r="F125" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B126">
         <v>16823</v>
@@ -7487,12 +7487,12 @@
         <v>1</v>
       </c>
       <c r="F126" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B127">
         <v>17033</v>
@@ -7507,12 +7507,12 @@
         <v>1</v>
       </c>
       <c r="F127" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B128">
         <v>17209</v>
@@ -7527,12 +7527,12 @@
         <v>1</v>
       </c>
       <c r="F128" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B129">
         <v>15905</v>
@@ -7547,12 +7547,12 @@
         <v>1</v>
       </c>
       <c r="F129" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B130">
         <v>16161</v>
@@ -7567,12 +7567,12 @@
         <v>1</v>
       </c>
       <c r="F130" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B131">
         <v>15855</v>
@@ -7587,12 +7587,12 @@
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B132">
         <v>17034</v>
@@ -7607,12 +7607,12 @@
         <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B133">
         <v>17207</v>
@@ -7627,12 +7627,12 @@
         <v>1</v>
       </c>
       <c r="F133" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B134">
         <v>17390</v>
@@ -7647,12 +7647,12 @@
         <v>1</v>
       </c>
       <c r="F134" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B135">
         <v>22603</v>
@@ -7667,12 +7667,12 @@
         <v>1</v>
       </c>
       <c r="F135" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B136">
         <v>22807</v>
@@ -7687,12 +7687,12 @@
         <v>1</v>
       </c>
       <c r="F136" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B137">
         <v>23140</v>
@@ -7707,12 +7707,12 @@
         <v>2</v>
       </c>
       <c r="F137" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B138">
         <v>23979</v>
@@ -7727,12 +7727,12 @@
         <v>2</v>
       </c>
       <c r="F138" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B139">
         <v>24163</v>
@@ -7747,12 +7747,12 @@
         <v>1</v>
       </c>
       <c r="F139" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B140">
         <v>24383</v>
@@ -7767,12 +7767,12 @@
         <v>2</v>
       </c>
       <c r="F140" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B141">
         <v>22725</v>
@@ -7787,12 +7787,12 @@
         <v>2</v>
       </c>
       <c r="F141" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B142">
         <v>23027</v>
@@ -7807,12 +7807,12 @@
         <v>3</v>
       </c>
       <c r="F142" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B143">
         <v>23250</v>
@@ -7827,12 +7827,12 @@
         <v>3</v>
       </c>
       <c r="F143" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B144">
         <v>23507</v>
@@ -7847,12 +7847,12 @@
         <v>3</v>
       </c>
       <c r="F144" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B145">
         <v>23161</v>
@@ -7867,12 +7867,12 @@
         <v>2</v>
       </c>
       <c r="F145" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B146">
         <v>23179</v>
@@ -7887,12 +7887,12 @@
         <v>2</v>
       </c>
       <c r="F146" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B147">
         <v>23625</v>
@@ -7907,12 +7907,12 @@
         <v>1</v>
       </c>
       <c r="F147" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B148">
         <v>23939</v>
@@ -7927,12 +7927,12 @@
         <v>2</v>
       </c>
       <c r="F148" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B149">
         <v>22559</v>
@@ -7947,12 +7947,12 @@
         <v>1</v>
       </c>
       <c r="F149" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B150">
         <v>23643</v>
@@ -7967,12 +7967,12 @@
         <v>1</v>
       </c>
       <c r="F150" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B151">
         <v>23843</v>
@@ -7987,12 +7987,12 @@
         <v>1</v>
       </c>
       <c r="F151" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B152">
         <v>24005</v>
@@ -8007,12 +8007,12 @@
         <v>1</v>
       </c>
       <c r="F152" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B153">
         <v>24364</v>
@@ -8027,12 +8027,12 @@
         <v>1</v>
       </c>
       <c r="F153" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B154">
         <v>24887</v>
@@ -8047,12 +8047,12 @@
         <v>1</v>
       </c>
       <c r="F154" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B155">
         <v>25080</v>
@@ -8067,12 +8067,12 @@
         <v>1</v>
       </c>
       <c r="F155" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B156">
         <v>25256</v>
@@ -8087,12 +8087,12 @@
         <v>1</v>
       </c>
       <c r="F156" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B157">
         <v>25536</v>
@@ -8107,12 +8107,12 @@
         <v>1</v>
       </c>
       <c r="F157" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B158">
         <v>23963</v>
@@ -8127,12 +8127,12 @@
         <v>1</v>
       </c>
       <c r="F158" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B159">
         <v>24121</v>
@@ -8147,12 +8147,12 @@
         <v>1</v>
       </c>
       <c r="F159" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B160">
         <v>24332</v>
@@ -8167,12 +8167,12 @@
         <v>1</v>
       </c>
       <c r="F160" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B161">
         <v>25015</v>
@@ -8187,12 +8187,12 @@
         <v>1</v>
       </c>
       <c r="F161" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B162">
         <v>25181</v>
@@ -8207,12 +8207,12 @@
         <v>1</v>
       </c>
       <c r="F162" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B163">
         <v>24507</v>
@@ -8227,12 +8227,12 @@
         <v>2</v>
       </c>
       <c r="F163" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B164">
         <v>24684</v>
@@ -8247,12 +8247,12 @@
         <v>2</v>
       </c>
       <c r="F164" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B165">
         <v>24880</v>
@@ -8267,12 +8267,12 @@
         <v>2</v>
       </c>
       <c r="F165" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B166">
         <v>25126</v>
@@ -8287,12 +8287,12 @@
         <v>2</v>
       </c>
       <c r="F166" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B167">
         <v>25323</v>
@@ -8307,12 +8307,12 @@
         <v>2</v>
       </c>
       <c r="F167" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B168">
         <v>25899</v>
@@ -8327,12 +8327,12 @@
         <v>2</v>
       </c>
       <c r="F168" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B169">
         <v>26072</v>
@@ -8347,12 +8347,12 @@
         <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B170">
         <v>24793</v>
@@ -8367,12 +8367,12 @@
         <v>1</v>
       </c>
       <c r="F170" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B171">
         <v>25394</v>
@@ -8387,12 +8387,12 @@
         <v>1</v>
       </c>
       <c r="F171" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B172">
         <v>26189</v>
@@ -8407,12 +8407,12 @@
         <v>1</v>
       </c>
       <c r="F172" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B173">
         <v>26383</v>
@@ -8427,12 +8427,12 @@
         <v>1</v>
       </c>
       <c r="F173" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B174">
         <v>26575</v>
@@ -8447,12 +8447,12 @@
         <v>1</v>
       </c>
       <c r="F174" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B175">
         <v>24496</v>
@@ -8467,12 +8467,12 @@
         <v>1</v>
       </c>
       <c r="F175" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B176">
         <v>25891</v>
@@ -8487,12 +8487,12 @@
         <v>0</v>
       </c>
       <c r="F176" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B177">
         <v>24307</v>
@@ -8507,12 +8507,12 @@
         <v>2</v>
       </c>
       <c r="F177" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B178">
         <v>26312</v>
@@ -8527,12 +8527,12 @@
         <v>1</v>
       </c>
       <c r="F178" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B179">
         <v>26509</v>
@@ -8547,12 +8547,12 @@
         <v>1</v>
       </c>
       <c r="F179" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B180">
         <v>24408</v>
@@ -8567,12 +8567,12 @@
         <v>1</v>
       </c>
       <c r="F180" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B181">
         <v>24721</v>
@@ -8587,12 +8587,12 @@
         <v>1</v>
       </c>
       <c r="F181" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B182">
         <v>25406</v>
@@ -8607,12 +8607,12 @@
         <v>0</v>
       </c>
       <c r="F182" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B183">
         <v>26084</v>
@@ -8627,12 +8627,12 @@
         <v>1</v>
       </c>
       <c r="F183" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B184">
         <v>24225</v>
@@ -8647,12 +8647,12 @@
         <v>2</v>
       </c>
       <c r="F184" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B185">
         <v>25228</v>
@@ -8667,12 +8667,12 @@
         <v>2</v>
       </c>
       <c r="F185" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B186">
         <v>25552</v>
@@ -8687,12 +8687,12 @@
         <v>2</v>
       </c>
       <c r="F186" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B187">
         <v>24794</v>
@@ -8707,12 +8707,12 @@
         <v>2</v>
       </c>
       <c r="F187" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B188">
         <v>19739</v>
@@ -8727,12 +8727,12 @@
         <v>1</v>
       </c>
       <c r="F188" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B189">
         <v>19927</v>
@@ -8747,12 +8747,12 @@
         <v>1</v>
       </c>
       <c r="F189" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B190">
         <v>20111</v>
@@ -8767,12 +8767,12 @@
         <v>1</v>
       </c>
       <c r="F190" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B191">
         <v>20306</v>
@@ -8787,12 +8787,12 @@
         <v>1</v>
       </c>
       <c r="F191" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B192">
         <v>21126</v>
@@ -8807,12 +8807,12 @@
         <v>1</v>
       </c>
       <c r="F192" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B193">
         <v>21315</v>
@@ -8827,12 +8827,12 @@
         <v>1</v>
       </c>
       <c r="F193" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B194">
         <v>19937</v>
@@ -8847,12 +8847,12 @@
         <v>0</v>
       </c>
       <c r="F194" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B195">
         <v>20114</v>
@@ -8867,12 +8867,12 @@
         <v>1</v>
       </c>
       <c r="F195" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B196">
         <v>21259</v>
@@ -8887,12 +8887,12 @@
         <v>1</v>
       </c>
       <c r="F196" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B197">
         <v>12651</v>
@@ -8907,12 +8907,12 @@
         <v>0</v>
       </c>
       <c r="F197" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B198">
         <v>12819</v>
@@ -8927,12 +8927,12 @@
         <v>0</v>
       </c>
       <c r="F198" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B199">
         <v>12997</v>
@@ -8947,12 +8947,12 @@
         <v>0</v>
       </c>
       <c r="F199" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B200">
         <v>13189</v>
@@ -8967,12 +8967,12 @@
         <v>1</v>
       </c>
       <c r="F200" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B201">
         <v>13353</v>
@@ -8987,12 +8987,12 @@
         <v>0</v>
       </c>
       <c r="F201" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B202">
         <v>14193</v>
@@ -9007,12 +9007,12 @@
         <v>0</v>
       </c>
       <c r="F202" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B203">
         <v>14373</v>
@@ -9027,12 +9027,12 @@
         <v>0</v>
       </c>
       <c r="F203" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B204">
         <v>14533</v>
@@ -9047,12 +9047,12 @@
         <v>0</v>
       </c>
       <c r="F204" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B205">
         <v>14337</v>
@@ -9067,12 +9067,12 @@
         <v>0</v>
       </c>
       <c r="F205" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B206">
         <v>14503</v>
@@ -9087,12 +9087,12 @@
         <v>0</v>
       </c>
       <c r="F206" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B207">
         <v>15548</v>
@@ -9107,12 +9107,12 @@
         <v>0</v>
       </c>
       <c r="F207" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B208">
         <v>16126</v>
@@ -9127,12 +9127,12 @@
         <v>0</v>
       </c>
       <c r="F208" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B209">
         <v>16296</v>
@@ -9147,12 +9147,12 @@
         <v>0</v>
       </c>
       <c r="F209" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B210">
         <v>16625</v>
@@ -9167,12 +9167,12 @@
         <v>0</v>
       </c>
       <c r="F210" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B211">
         <v>17746</v>
@@ -9187,12 +9187,12 @@
         <v>0</v>
       </c>
       <c r="F211" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B212">
         <v>18369</v>
@@ -9207,12 +9207,12 @@
         <v>0</v>
       </c>
       <c r="F212" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B213">
         <v>16463</v>
@@ -9227,12 +9227,12 @@
         <v>1</v>
       </c>
       <c r="F213" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B214">
         <v>16798</v>
@@ -9247,12 +9247,12 @@
         <v>1</v>
       </c>
       <c r="F214" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B215">
         <v>16962</v>
@@ -9267,12 +9267,12 @@
         <v>1</v>
       </c>
       <c r="F215" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B216">
         <v>17584</v>
@@ -9287,12 +9287,12 @@
         <v>1</v>
       </c>
       <c r="F216" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B217">
         <v>18173</v>
@@ -9307,12 +9307,12 @@
         <v>1</v>
       </c>
       <c r="F217" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B218">
         <v>23728</v>
@@ -9327,12 +9327,12 @@
         <v>1</v>
       </c>
       <c r="F218" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B219">
         <v>16692</v>
@@ -9347,12 +9347,12 @@
         <v>0</v>
       </c>
       <c r="F219" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B220">
         <v>14768</v>
@@ -9367,12 +9367,12 @@
         <v>1</v>
       </c>
       <c r="F220" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B221">
         <v>14945</v>
@@ -9387,12 +9387,12 @@
         <v>1</v>
       </c>
       <c r="F221" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B222">
         <v>16365</v>
@@ -9407,12 +9407,12 @@
         <v>1</v>
       </c>
       <c r="F222" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B223">
         <v>17785</v>
@@ -9427,12 +9427,12 @@
         <v>1</v>
       </c>
       <c r="F223" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B224">
         <v>18661</v>
@@ -9447,12 +9447,12 @@
         <v>1</v>
       </c>
       <c r="F224" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B225">
         <v>19593</v>
@@ -9467,12 +9467,12 @@
         <v>0</v>
       </c>
       <c r="F225" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B226">
         <v>18081</v>
@@ -9487,12 +9487,12 @@
         <v>1</v>
       </c>
       <c r="F226" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B227">
         <v>18242</v>
@@ -9507,12 +9507,12 @@
         <v>1</v>
       </c>
       <c r="F227" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B228">
         <v>18426</v>
@@ -9527,12 +9527,12 @@
         <v>1</v>
       </c>
       <c r="F228" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B229">
         <v>19269</v>
@@ -9547,12 +9547,12 @@
         <v>1</v>
       </c>
       <c r="F229" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B230">
         <v>19441</v>
@@ -9567,12 +9567,12 @@
         <v>1</v>
       </c>
       <c r="F230" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B231">
         <v>18252</v>
@@ -9587,12 +9587,12 @@
         <v>1</v>
       </c>
       <c r="F231" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B232">
         <v>19836</v>
@@ -9607,12 +9607,12 @@
         <v>1</v>
       </c>
       <c r="F232" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B233">
         <v>20004</v>
@@ -9627,12 +9627,12 @@
         <v>1</v>
       </c>
       <c r="F233" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B234">
         <v>21145</v>
@@ -9647,12 +9647,12 @@
         <v>0</v>
       </c>
       <c r="F234" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B235">
         <v>21603</v>
@@ -9667,12 +9667,12 @@
         <v>0</v>
       </c>
       <c r="F235" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B236">
         <v>19843</v>
@@ -9687,12 +9687,12 @@
         <v>1</v>
       </c>
       <c r="F236" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B237">
         <v>20012</v>
@@ -9707,12 +9707,12 @@
         <v>1</v>
       </c>
       <c r="F237" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B238">
         <v>19826</v>
@@ -9727,12 +9727,12 @@
         <v>1</v>
       </c>
       <c r="F238" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B239">
         <v>19855</v>
@@ -9747,12 +9747,12 @@
         <v>1</v>
       </c>
       <c r="F239" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B240">
         <v>21864</v>
@@ -9767,12 +9767,12 @@
         <v>1</v>
       </c>
       <c r="F240" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B241">
         <v>22083</v>
@@ -9787,12 +9787,12 @@
         <v>0</v>
       </c>
       <c r="F241" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B242">
         <v>22285</v>
@@ -9807,12 +9807,12 @@
         <v>1</v>
       </c>
       <c r="F242" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B243">
         <v>23039</v>
@@ -9827,12 +9827,12 @@
         <v>1</v>
       </c>
       <c r="F243" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B244">
         <v>23216</v>
@@ -9847,12 +9847,12 @@
         <v>1</v>
       </c>
       <c r="F244" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B245">
         <v>21827</v>
@@ -9867,12 +9867,12 @@
         <v>1</v>
       </c>
       <c r="F245" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B246">
         <v>22045</v>
@@ -9887,12 +9887,12 @@
         <v>1</v>
       </c>
       <c r="F246" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B247">
         <v>21871</v>
@@ -9907,12 +9907,12 @@
         <v>1</v>
       </c>
       <c r="F247" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B248">
         <v>21975</v>
@@ -9927,12 +9927,12 @@
         <v>1</v>
       </c>
       <c r="F248" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="249" spans="1:6">
       <c r="A249" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B249">
         <v>22374</v>
@@ -9947,12 +9947,12 @@
         <v>1</v>
       </c>
       <c r="F249" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B250">
         <v>22493</v>
@@ -9967,12 +9967,12 @@
         <v>1</v>
       </c>
       <c r="F250" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B251">
         <v>23282</v>
@@ -9987,12 +9987,12 @@
         <v>1</v>
       </c>
       <c r="F251" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B252">
         <v>22832</v>
@@ -10007,12 +10007,12 @@
         <v>1</v>
       </c>
       <c r="F252" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B253">
         <v>24019</v>
@@ -10027,12 +10027,12 @@
         <v>2</v>
       </c>
       <c r="F253" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B254">
         <v>29349</v>
@@ -10047,7 +10047,7 @@
         <v>2</v>
       </c>
       <c r="F254" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -10070,15 +10070,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B1" t="s">
         <v>197</v>
-      </c>
-      <c r="B1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B2" s="10">
         <v>45557</v>
@@ -10086,48 +10086,48 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4" t="s">
         <v>201</v>
-      </c>
-      <c r="B4" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="66">
       <c r="B11" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="B13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -10147,7 +10147,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -10167,7 +10167,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -10187,12 +10187,12 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -10202,7 +10202,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="B26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -10221,28 +10221,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" t="s">
         <v>209</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>210</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>211</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>212</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>213</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>214</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>215</v>
-      </c>
-      <c r="H1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -11661,538 +11661,538 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B116" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B117" t="b">
         <v>0</v>
@@ -12200,7 +12200,7 @@
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B118" t="b">
         <v>0</v>
@@ -12208,7 +12208,7 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B119" t="b">
         <v>0</v>
@@ -12216,7 +12216,7 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B120" t="b">
         <v>0</v>
@@ -12224,7 +12224,7 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B121" t="b">
         <v>0</v>
@@ -12232,7 +12232,7 @@
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B122" t="s">
         <v>22</v>
@@ -12240,7 +12240,7 @@
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B123" t="b">
         <v>1</v>
@@ -12248,7 +12248,7 @@
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B124" t="b">
         <v>0</v>
@@ -12256,7 +12256,7 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B125" t="b">
         <v>1</v>
@@ -12264,7 +12264,7 @@
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B126" t="s">
         <v>22</v>
@@ -12272,7 +12272,7 @@
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B127" t="s">
         <v>22</v>
@@ -12280,7 +12280,7 @@
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B128" t="s">
         <v>22</v>
@@ -12288,7 +12288,7 @@
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B129" t="s">
         <v>22</v>
@@ -12296,7 +12296,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B130" t="s">
         <v>22</v>
@@ -12304,7 +12304,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B131" t="b">
         <v>0</v>
@@ -12312,7 +12312,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B132" t="b">
         <v>1</v>
@@ -12320,7 +12320,7 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B133" t="b">
         <v>1</v>
@@ -12328,7 +12328,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B134" t="s">
         <v>22</v>
@@ -12336,7 +12336,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B135" t="s">
         <v>22</v>
@@ -12344,7 +12344,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B136" t="s">
         <v>22</v>
@@ -12352,7 +12352,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B137" t="b">
         <v>0</v>
